--- a/artfynd/A 25528-2024 artfynd.xlsx
+++ b/artfynd/A 25528-2024 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113590415</v>
+        <v>113598573</v>
       </c>
       <c r="B2" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Naturen, Nb</t>
+          <t>Luleå, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>818255</v>
+        <v>818075</v>
       </c>
       <c r="R2" t="n">
-        <v>7289379</v>
+        <v>7289332</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Hagsand</t>
+          <t>Linnea Åsedahl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 25528-2024 artfynd.xlsx
+++ b/artfynd/A 25528-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,8 +774,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113598573</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>